--- a/sample_data/cons_mei.xlsx
+++ b/sample_data/cons_mei.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PAYROLL SYSTEM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\laragon\www\instance1.uranop.com\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4B0C51-5511-4B51-B174-0380DF5A74DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717A6E96-353C-4002-81BC-F385667A5241}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7CCB7C8B-9F4E-438D-96B6-275C440D85CF}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{7CCB7C8B-9F4E-438D-96B6-275C440D85CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1457,20 +1454,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1478,11 +1470,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1812,7 +1819,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="2" width="37.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -1823,618 +1830,448 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="6">
         <v>1</v>
       </c>
-      <c r="D1" s="9">
+      <c r="D1" s="6">
         <v>2</v>
       </c>
-      <c r="E1" s="9">
+      <c r="E1" s="6">
         <v>3</v>
       </c>
-      <c r="F1" s="9">
+      <c r="F1" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>46147</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>46137</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>46151</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>46162</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>46163</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>46160</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>46153</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>46157</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>46149</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>46154</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>46142</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>46160</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    </row>
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>46147</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>46157</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+    </row>
+    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    </row>
+    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    </row>
+    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    </row>
+    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+    </row>
+    <row r="34" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    </row>
+    <row r="36" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    </row>
+    <row r="37" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+    </row>
+    <row r="38" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+    </row>
+    <row r="39" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+    </row>
+    <row r="40" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+    </row>
+    <row r="41" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="5">
         <v>46139</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+    </row>
+    <row r="42" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="5">
         <v>46147</v>
       </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+    </row>
+    <row r="43" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="5">
         <v>46163</v>
       </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
+    </row>
+    <row r="44" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="5">
         <v>46165</v>
       </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+    </row>
+    <row r="45" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+    </row>
+    <row r="46" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+    </row>
+    <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+    </row>
+    <row r="48" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
@@ -2579,16 +2416,16 @@
       <c r="B66" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="5">
         <v>46151</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="5">
         <v>46157</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="5">
         <v>46158</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="5">
         <v>46162</v>
       </c>
     </row>
@@ -2623,7 +2460,7 @@
       <c r="B70" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="5">
         <v>46155</v>
       </c>
     </row>
@@ -2650,7 +2487,7 @@
       <c r="B73" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="5">
         <v>46139</v>
       </c>
     </row>
@@ -2685,7 +2522,7 @@
       <c r="B77" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="5">
         <v>46151</v>
       </c>
     </row>
@@ -2696,10 +2533,10 @@
       <c r="B78" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="5">
         <v>46149</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="5">
         <v>46160</v>
       </c>
     </row>
@@ -2710,10 +2547,10 @@
       <c r="B79" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="5">
         <v>46144</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="5">
         <v>46164</v>
       </c>
     </row>
@@ -2724,7 +2561,7 @@
       <c r="B80" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="5">
         <v>46164</v>
       </c>
     </row>
@@ -2735,10 +2572,10 @@
       <c r="B81" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="5">
         <v>46147</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="5">
         <v>46161</v>
       </c>
     </row>
@@ -2749,7 +2586,7 @@
       <c r="B82" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C82" s="8">
+      <c r="C82" s="5">
         <v>46161</v>
       </c>
     </row>
@@ -2760,7 +2597,7 @@
       <c r="B83" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C83" s="8">
+      <c r="C83" s="5">
         <v>46160</v>
       </c>
     </row>
@@ -2771,10 +2608,10 @@
       <c r="B84" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="5">
         <v>46153</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="5">
         <v>46154</v>
       </c>
     </row>
@@ -2785,7 +2622,6 @@
       <c r="B85" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C85" s="7"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
@@ -2794,10 +2630,10 @@
       <c r="B86" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C86" s="8">
+      <c r="C86" s="5">
         <v>46140</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="5">
         <v>46160</v>
       </c>
     </row>
@@ -2808,7 +2644,7 @@
       <c r="B87" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="5">
         <v>46165</v>
       </c>
     </row>
@@ -2835,7 +2671,7 @@
       <c r="B90" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="5">
         <v>46151</v>
       </c>
     </row>
@@ -2854,7 +2690,7 @@
       <c r="B92" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="5">
         <v>46165</v>
       </c>
     </row>
@@ -2873,7 +2709,7 @@
       <c r="B94" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="5">
         <v>46164</v>
       </c>
     </row>
@@ -2884,7 +2720,7 @@
       <c r="B95" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="5">
         <v>46146</v>
       </c>
     </row>
@@ -2919,13 +2755,13 @@
       <c r="B99" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="5">
         <v>46163</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="5">
         <v>46164</v>
       </c>
-      <c r="E99" s="7">
+      <c r="E99" s="5">
         <v>46165</v>
       </c>
     </row>
@@ -2936,7 +2772,7 @@
       <c r="B100" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="5">
         <v>46165</v>
       </c>
     </row>
@@ -2947,7 +2783,7 @@
       <c r="B101" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="5">
         <v>46147</v>
       </c>
     </row>
@@ -2958,7 +2794,6 @@
       <c r="B102" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C102" s="7"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
@@ -2991,7 +2826,7 @@
       <c r="B106" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="5">
         <v>46154</v>
       </c>
     </row>
@@ -3002,7 +2837,6 @@
       <c r="B107" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C107" s="7"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
@@ -3019,7 +2853,6 @@
       <c r="B109" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C109" s="7"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
@@ -3028,7 +2861,6 @@
       <c r="B110" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C110" s="7"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
@@ -3037,10 +2869,10 @@
       <c r="B111" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C111" s="8">
+      <c r="C111" s="5">
         <v>46161</v>
       </c>
-      <c r="D111" s="7">
+      <c r="D111" s="5">
         <v>46162</v>
       </c>
     </row>
@@ -3059,7 +2891,6 @@
       <c r="B113" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C113" s="7"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
@@ -3076,7 +2907,7 @@
       <c r="B115" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="5">
         <v>46162</v>
       </c>
     </row>
@@ -3095,13 +2926,13 @@
       <c r="B117" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C117" s="8">
+      <c r="C117" s="5">
         <v>46137</v>
       </c>
-      <c r="D117" s="7">
+      <c r="D117" s="5">
         <v>46139</v>
       </c>
-      <c r="E117" s="8">
+      <c r="E117" s="5">
         <v>46144</v>
       </c>
     </row>
@@ -3120,7 +2951,7 @@
       <c r="B119" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="5">
         <v>46146</v>
       </c>
     </row>
@@ -3147,13 +2978,13 @@
       <c r="B122" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="5">
         <v>46141</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="5">
         <v>46142</v>
       </c>
-      <c r="E122" s="7">
+      <c r="E122" s="5">
         <v>46165</v>
       </c>
     </row>
@@ -3164,10 +2995,10 @@
       <c r="B123" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C123" s="8">
+      <c r="C123" s="5">
         <v>46140</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D123" s="5">
         <v>46160</v>
       </c>
     </row>
@@ -3194,7 +3025,7 @@
       <c r="B126" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="5">
         <v>46148</v>
       </c>
     </row>
@@ -3214,16 +3045,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>304</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C129" s="7"/>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>305</v>
       </c>
@@ -3231,7 +3061,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>306</v>
       </c>
@@ -3239,7 +3069,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>307</v>
       </c>
@@ -3247,7 +3077,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>308</v>
       </c>
@@ -3255,7 +3085,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>309</v>
       </c>
@@ -3263,7 +3093,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>310</v>
       </c>
@@ -3271,7 +3101,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>311</v>
       </c>
@@ -3279,7 +3109,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>312</v>
       </c>
@@ -3287,27 +3117,26 @@
         <v>185</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>313</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C138" s="7"/>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>314</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="5">
         <v>46142</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>315</v>
       </c>
@@ -3315,17 +3144,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>316</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>317</v>
       </c>
@@ -3333,7 +3160,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>318</v>
       </c>
@@ -3341,7 +3168,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>319</v>
       </c>
@@ -3396,7 +3223,7 @@
       <c r="B150" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="5">
         <v>46148</v>
       </c>
     </row>
@@ -3423,7 +3250,7 @@
       <c r="B153" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C153" s="8">
+      <c r="C153" s="5">
         <v>46155</v>
       </c>
     </row>
@@ -3442,7 +3269,7 @@
       <c r="B155" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C155" s="8">
+      <c r="C155" s="5">
         <v>46158</v>
       </c>
     </row>
@@ -3469,7 +3296,7 @@
       <c r="B158" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C158" s="7">
+      <c r="C158" s="5">
         <v>46149</v>
       </c>
     </row>
@@ -3480,7 +3307,7 @@
       <c r="B159" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C159" s="7">
+      <c r="C159" s="5">
         <v>46151</v>
       </c>
     </row>
@@ -3491,7 +3318,7 @@
       <c r="B160" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C160" s="7">
+      <c r="C160" s="5">
         <v>46165</v>
       </c>
     </row>
@@ -3502,10 +3329,10 @@
       <c r="B161" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C161" s="8">
+      <c r="C161" s="5">
         <v>46140</v>
       </c>
-      <c r="D161" s="7">
+      <c r="D161" s="5">
         <v>46154</v>
       </c>
     </row>
@@ -3588,7 +3415,7 @@
       <c r="B171" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C171" s="8">
+      <c r="C171" s="5">
         <v>46155</v>
       </c>
     </row>
@@ -3599,7 +3426,7 @@
       <c r="B172" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C172" s="8">
+      <c r="C172" s="5">
         <v>46144</v>
       </c>
     </row>
@@ -3628,7 +3455,7 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="4" t="s">
         <v>376</v>
       </c>
       <c r="B176" s="3" t="s">
@@ -3636,7 +3463,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
+      <c r="A177" s="4" t="s">
         <v>377</v>
       </c>
       <c r="B177" s="3" t="s">
@@ -3644,7 +3471,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="4" t="s">
         <v>378</v>
       </c>
       <c r="B178" s="3" t="s">
@@ -3652,7 +3479,7 @@
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="4" t="s">
         <v>379</v>
       </c>
       <c r="B179" s="3" t="s">
@@ -3660,7 +3487,7 @@
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="6" t="s">
+      <c r="A180" s="4" t="s">
         <v>380</v>
       </c>
       <c r="B180" s="3" t="s">
@@ -3668,7 +3495,7 @@
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="6" t="s">
+      <c r="A181" s="4" t="s">
         <v>381</v>
       </c>
       <c r="B181" s="3" t="s">
@@ -3676,7 +3503,7 @@
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="4" t="s">
         <v>382</v>
       </c>
       <c r="B182" s="3" t="s">
@@ -3684,7 +3511,7 @@
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="6" t="s">
+      <c r="A183" s="4" t="s">
         <v>383</v>
       </c>
       <c r="B183" s="3" t="s">
@@ -3692,7 +3519,7 @@
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="4" t="s">
         <v>384</v>
       </c>
       <c r="B184" s="3" t="s">
@@ -3700,7 +3527,7 @@
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="6" t="s">
+      <c r="A185" s="4" t="s">
         <v>385</v>
       </c>
       <c r="B185" s="3" t="s">
@@ -3708,7 +3535,7 @@
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="4" t="s">
         <v>386</v>
       </c>
       <c r="B186" s="3" t="s">
@@ -3716,7 +3543,7 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="6" t="s">
+      <c r="A187" s="4" t="s">
         <v>387</v>
       </c>
       <c r="B187" s="3" t="s">
@@ -3724,7 +3551,7 @@
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="4" t="s">
         <v>388</v>
       </c>
       <c r="B188" s="3" t="s">
@@ -3732,7 +3559,7 @@
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="6" t="s">
+      <c r="A189" s="4" t="s">
         <v>389</v>
       </c>
       <c r="B189" s="3" t="s">
@@ -3740,7 +3567,7 @@
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="4" t="s">
         <v>390</v>
       </c>
       <c r="B190" s="3" t="s">
@@ -3748,7 +3575,7 @@
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="6" t="s">
+      <c r="A191" s="4" t="s">
         <v>391</v>
       </c>
       <c r="B191" s="3" t="s">
@@ -3756,7 +3583,7 @@
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="6" t="s">
+      <c r="A192" s="4" t="s">
         <v>392</v>
       </c>
       <c r="B192" s="3" t="s">
@@ -3764,7 +3591,7 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>34</v>
       </c>
       <c r="B193" s="3" t="s">
@@ -3772,7 +3599,7 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>35</v>
       </c>
       <c r="B194" s="3" t="s">
@@ -3780,7 +3607,7 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" s="6" t="s">
+      <c r="A195" s="4" t="s">
         <v>393</v>
       </c>
       <c r="B195" s="3" t="s">
@@ -3788,7 +3615,7 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="6" t="s">
+      <c r="A196" s="4" t="s">
         <v>394</v>
       </c>
       <c r="B196" s="3" t="s">
@@ -3796,7 +3623,7 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" s="6" t="s">
+      <c r="A197" s="4" t="s">
         <v>395</v>
       </c>
       <c r="B197" s="3" t="s">
@@ -3804,7 +3631,7 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198" s="6">
+      <c r="A198" s="4">
         <v>424</v>
       </c>
       <c r="B198" s="3" t="s">
@@ -3812,7 +3639,7 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199" s="6" t="s">
+      <c r="A199" s="4" t="s">
         <v>396</v>
       </c>
       <c r="B199" s="3" t="s">
@@ -3820,7 +3647,7 @@
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A200" s="6" t="s">
+      <c r="A200" s="4" t="s">
         <v>397</v>
       </c>
       <c r="B200" s="3" t="s">
@@ -3828,7 +3655,7 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A201" s="6" t="s">
+      <c r="A201" s="4" t="s">
         <v>398</v>
       </c>
       <c r="B201" s="3" t="s">
@@ -3836,18 +3663,18 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A202" s="6" t="s">
+      <c r="A202" s="4" t="s">
         <v>425</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C202" s="8">
+      <c r="C202" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A203" s="6" t="s">
+      <c r="A203" s="4" t="s">
         <v>426</v>
       </c>
       <c r="B203" s="3" t="s">
@@ -3855,7 +3682,7 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A204" s="6" t="s">
+      <c r="A204" s="4" t="s">
         <v>427</v>
       </c>
       <c r="B204" s="3" t="s">
@@ -3863,7 +3690,7 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A205" s="6" t="s">
+      <c r="A205" s="4" t="s">
         <v>428</v>
       </c>
       <c r="B205" s="3" t="s">
@@ -3871,21 +3698,21 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="4" t="s">
         <v>429</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C206" s="8">
+      <c r="C206" s="5">
         <v>46157</v>
       </c>
-      <c r="D206" s="8">
+      <c r="D206" s="5">
         <v>46161</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A207" s="6" t="s">
+      <c r="A207" s="4" t="s">
         <v>430</v>
       </c>
       <c r="B207" s="3" t="s">
@@ -3893,7 +3720,7 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A208" s="6" t="s">
+      <c r="A208" s="4" t="s">
         <v>431</v>
       </c>
       <c r="B208" s="3" t="s">
@@ -3901,7 +3728,7 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="6" t="s">
+      <c r="A209" s="4" t="s">
         <v>432</v>
       </c>
       <c r="B209" s="3" t="s">
@@ -3909,7 +3736,7 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" s="6" t="s">
+      <c r="A210" s="4" t="s">
         <v>433</v>
       </c>
       <c r="B210" s="3" t="s">
@@ -3917,18 +3744,18 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" s="6" t="s">
+      <c r="A211" s="4" t="s">
         <v>434</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C211" s="8">
+      <c r="C211" s="5">
         <v>46154</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" s="6" t="s">
+      <c r="A212" s="4" t="s">
         <v>435</v>
       </c>
       <c r="B212" s="3" t="s">
@@ -3936,7 +3763,7 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" s="6" t="s">
+      <c r="A213" s="4" t="s">
         <v>436</v>
       </c>
       <c r="B213" s="3" t="s">
@@ -3944,18 +3771,18 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="4" t="s">
         <v>437</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C214" s="7">
+      <c r="C214" s="5">
         <v>46163</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="4" t="s">
         <v>438</v>
       </c>
       <c r="B215" s="3" t="s">
@@ -3963,7 +3790,7 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="4" t="s">
         <v>439</v>
       </c>
       <c r="B216" s="3" t="s">
@@ -4033,10 +3860,10 @@
       <c r="B224" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C224" s="8">
+      <c r="C224" s="5">
         <v>46142</v>
       </c>
-      <c r="D224" s="8">
+      <c r="D224" s="5">
         <v>46158</v>
       </c>
     </row>
@@ -4057,7 +3884,7 @@
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A227" s="6">
+      <c r="A227" s="4">
         <v>422</v>
       </c>
       <c r="B227" s="3" t="s">
